--- a/DataframeCorrel.xlsx
+++ b/DataframeCorrel.xlsx
@@ -55,9 +55,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFD6D5D4"/>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,21 +68,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -91,10 +82,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -379,6 +368,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -393,11 +385,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -408,13 +400,13 @@
         <v>32.1</v>
       </c>
       <c r="D2">
-        <v>1950</v>
-      </c>
-      <c r="E2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="2">
         <v>122484</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -425,13 +417,13 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>1965</v>
-      </c>
-      <c r="E3" s="1">
+        <v>1230</v>
+      </c>
+      <c r="E3" s="2">
         <v>119309</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -442,13 +434,13 @@
         <v>31.8</v>
       </c>
       <c r="D4">
-        <v>1940</v>
-      </c>
-      <c r="E4" s="1">
+        <v>1200</v>
+      </c>
+      <c r="E4" s="2">
         <v>123238</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -459,13 +451,13 @@
         <v>34.200000000000003</v>
       </c>
       <c r="D5">
-        <v>1975</v>
-      </c>
-      <c r="E5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="E5" s="2">
         <v>127615</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -476,13 +468,13 @@
         <v>30.9</v>
       </c>
       <c r="D6">
-        <v>1930</v>
-      </c>
-      <c r="E6" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E6" s="2">
         <v>118829</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -495,11 +487,11 @@
       <c r="D7">
         <v>1980</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>118829</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -512,11 +504,11 @@
       <c r="D8">
         <v>1958</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>127896</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -529,11 +521,11 @@
       <c r="D9">
         <v>1968</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>123837</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -546,11 +538,11 @@
       <c r="D10">
         <v>1938</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>117653</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -563,11 +555,11 @@
       <c r="D11">
         <v>1985</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>122713</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -580,11 +572,11 @@
       <c r="D12">
         <v>1990</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>117683</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -597,11 +589,11 @@
       <c r="D13">
         <v>1925</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>117671</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -614,11 +606,11 @@
       <c r="D14">
         <v>2000</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>121210</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -631,11 +623,11 @@
       <c r="D15">
         <v>1910</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>110434</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -648,11 +640,11 @@
       <c r="D16">
         <v>2005</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>111375</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -665,11 +657,11 @@
       <c r="D17">
         <v>1900</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>117189</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -682,11 +674,11 @@
       <c r="D18">
         <v>2015</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>114936</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -699,11 +691,11 @@
       <c r="D19">
         <v>1895</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>121571</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -716,11 +708,11 @@
       <c r="D20">
         <v>2020</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>115460</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -733,11 +725,11 @@
       <c r="D21">
         <v>1890</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>112938</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -750,11 +742,11 @@
       <c r="D22">
         <v>2025</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="2">
         <v>127328</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -767,11 +759,11 @@
       <c r="D23">
         <v>1885</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>118871</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -784,11 +776,11 @@
       <c r="D24">
         <v>2030</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>120338</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -801,11 +793,11 @@
       <c r="D25">
         <v>1880</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>112876</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -818,11 +810,11 @@
       <c r="D26">
         <v>2035</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="2">
         <v>117278</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -835,11 +827,11 @@
       <c r="D27">
         <v>1875</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>120555</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -852,11 +844,11 @@
       <c r="D28">
         <v>2040</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="2">
         <v>114245</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -869,11 +861,11 @@
       <c r="D29">
         <v>1870</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>121878</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -886,11 +878,11 @@
       <c r="D30">
         <v>2045</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>116997</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -903,11 +895,11 @@
       <c r="D31">
         <v>1865</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <v>118542</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -920,11 +912,11 @@
       <c r="D32">
         <v>2050</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>116991</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -937,11 +929,11 @@
       <c r="D33">
         <v>1860</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>129261</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -954,11 +946,11 @@
       <c r="D34">
         <v>2055</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>119933</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -971,11 +963,11 @@
       <c r="D35">
         <v>1855</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>114711</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -988,11 +980,11 @@
       <c r="D36">
         <v>2060</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>124113</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1005,11 +997,11 @@
       <c r="D37">
         <v>1850</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>113896</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1022,11 +1014,11 @@
       <c r="D38">
         <v>2065</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>121044</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1039,11 +1031,11 @@
       <c r="D39">
         <v>1845</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>110202</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1056,11 +1048,11 @@
       <c r="D40">
         <v>2070</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>113359</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1073,11 +1065,11 @@
       <c r="D41">
         <v>1840</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>120984</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1090,11 +1082,11 @@
       <c r="D42">
         <v>2075</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>123692</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1107,11 +1099,11 @@
       <c r="D43">
         <v>1835</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="2">
         <v>120857</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1124,11 +1116,11 @@
       <c r="D44">
         <v>2080</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>119422</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1141,11 +1133,11 @@
       <c r="D45">
         <v>1830</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>118494</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1158,11 +1150,11 @@
       <c r="D46">
         <v>2085</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>112607</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1175,11 +1167,11 @@
       <c r="D47">
         <v>1825</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>116401</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1192,11 +1184,11 @@
       <c r="D48">
         <v>2090</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>117697</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1209,11 +1201,11 @@
       <c r="D49">
         <v>1820</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>125286</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1226,11 +1218,11 @@
       <c r="D50">
         <v>2095</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>121718</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
